--- a/Design/Excel/ET/Datas/Game/Scene.xlsx
+++ b/Design/Excel/ET/Datas/Game/Scene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1816DF57-C81C-44B1-BC5E-38B7B62A948B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EED2EBF-AA6B-4868-8B25-35787853617E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="场景配置表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>##var</t>
   </si>
@@ -93,9 +93,6 @@
   </si>
   <si>
     <t>Main</t>
-  </si>
-  <si>
-    <t>战斗场景</t>
   </si>
   <si>
     <t>Map2d</t>
@@ -103,6 +100,21 @@
   </si>
   <si>
     <t>2战斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MapFight</t>
+  </si>
+  <si>
+    <t>MapFight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>主场景</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -121,6 +133,7 @@
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -465,14 +478,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.90625" style="1"/>
     <col min="2" max="2" width="19.36328125" style="1" customWidth="1"/>
     <col min="3" max="3" width="23.36328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.08984375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="33.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="35.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.26953125" style="1" customWidth="1"/>
     <col min="7" max="16384" width="8.90625" style="1"/>
   </cols>
@@ -504,8 +517,8 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -561,8 +574,8 @@
       <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>20</v>
+      <c r="D5" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>19</v>
@@ -576,15 +589,32 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="1">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="1">
+      <c r="F7" s="1">
         <v>2</v>
       </c>
     </row>

--- a/Design/Excel/ET/Datas/Game/Scene.xlsx
+++ b/Design/Excel/ET/Datas/Game/Scene.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\ugit\myGameDevelopmentKit\Design\Excel\ET\Datas\Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EED2EBF-AA6B-4868-8B25-35787853617E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1306E70B-777D-467C-A739-122126651726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4530" yWindow="450" windowWidth="19200" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="场景配置表" sheetId="1" r:id="rId1"/>
